--- a/pds_admin_karnataka/Backend/Backend/Result_Sheet_F2.xlsx
+++ b/pds_admin_karnataka/Backend/Backend/Result_Sheet_F2.xlsx
@@ -148,7 +148,7 @@
     <t>K.K.LAMANI CHINCHALAKATTI L.T.</t>
   </si>
   <si>
-    <t>Millets</t>
+    <t>Ragi</t>
   </si>
 </sst>
 </file>
